--- a/9432.T_settings.xlsx
+++ b/9432.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -482,42 +497,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>7.612015055460088</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.543715361104292</v>
+      </c>
+      <c r="I2" t="n">
+        <v>76120.15055460087</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1076120.150554601</v>
+      </c>
+      <c r="K2" t="n">
+        <v>29308.54019465601</v>
+      </c>
+      <c r="L2" t="n">
+        <v>18.85714285714286</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.352170559005449</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -529,42 +545,43 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4.675039817605575</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3596184475081212</v>
+      </c>
+      <c r="I3" t="n">
+        <v>46750.39817605575</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1046750.398176056</v>
+      </c>
+      <c r="K3" t="n">
+        <v>27510.22189543437</v>
+      </c>
+      <c r="L3" t="n">
+        <v>22.76923076923077</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.376444474402588</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -585,33 +602,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3.007288486012688</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2506073738343907</v>
+      </c>
+      <c r="I4" t="n">
+        <v>30072.88486012688</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1030072.884860127</v>
+      </c>
+      <c r="K4" t="n">
+        <v>25845.40753178055</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11.63256599361263</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -623,42 +641,43 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.385650723548699</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1385650723548699</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13856.50723548699</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1013856.507235487</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20566.83720297617</v>
+      </c>
+      <c r="L5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10.42809822239414</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -670,42 +689,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.569661661519506</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.04382012780919277</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-5696.61661519506</v>
+      </c>
+      <c r="J6" t="n">
+        <v>994303.3833848049</v>
+      </c>
+      <c r="K6" t="n">
+        <v>28454.96331526446</v>
+      </c>
+      <c r="L6" t="n">
+        <v>22.30769230769231</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16.49227970951264</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -713,46 +733,47 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-2.005090074573061</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.2005090074573061</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-20050.90074573061</v>
+      </c>
+      <c r="J7" t="n">
+        <v>979949.0992542694</v>
+      </c>
+      <c r="K7" t="n">
+        <v>19701.08449518263</v>
+      </c>
+      <c r="L7" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11.19042233991907</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -760,11 +781,11 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -773,33 +794,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-2.428816998501623</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.2428816998501623</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-24288.16998501623</v>
+      </c>
+      <c r="J8" t="n">
+        <v>975711.8300149838</v>
+      </c>
+      <c r="K8" t="n">
+        <v>21601.66673592353</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14.51076576711587</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -811,7 +833,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -820,33 +842,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-2.79572114116723</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.279572114116723</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-27957.2114116723</v>
+      </c>
+      <c r="J9" t="n">
+        <v>972042.7885883277</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20127.9525420345</v>
+      </c>
+      <c r="L9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12.3088808570559</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -854,11 +877,11 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -867,33 +890,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-3.061452554666938</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1913407846666836</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-30614.52554666938</v>
+      </c>
+      <c r="J10" t="n">
+        <v>969385.4744533306</v>
+      </c>
+      <c r="K10" t="n">
+        <v>34968.14711857103</v>
+      </c>
+      <c r="L10" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20.3918454117041</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -901,46 +925,47 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-3.661507446657808</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.4068341607397564</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-36615.07446657808</v>
+      </c>
+      <c r="J11" t="n">
+        <v>963384.9255334219</v>
+      </c>
+      <c r="K11" t="n">
+        <v>17854.54448185549</v>
+      </c>
+      <c r="L11" t="n">
+        <v>21.11111111111111</v>
+      </c>
+      <c r="M11" t="n">
+        <v>13.14054133261224</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -948,46 +973,47 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-3.775275142113515</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2516850094742343</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-37752.75142113515</v>
+      </c>
+      <c r="J12" t="n">
+        <v>962247.2485788648</v>
+      </c>
+      <c r="K12" t="n">
+        <v>31867.63767788429</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>17.71773189272497</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -995,7 +1021,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1004,37 +1030,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-3.937079606202687</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2812199718716205</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-39370.79606202687</v>
+      </c>
+      <c r="J13" t="n">
+        <v>960629.2039379731</v>
+      </c>
+      <c r="K13" t="n">
+        <v>29342.33853733689</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.21428571428572</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17.721322054217</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1042,7 +1069,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1055,33 +1082,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-4.669751984537545</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.3113167989691696</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-46697.51984537544</v>
+      </c>
+      <c r="J14" t="n">
+        <v>953302.4801546246</v>
+      </c>
+      <c r="K14" t="n">
+        <v>31357.20834079523</v>
+      </c>
+      <c r="L14" t="n">
+        <v>18.26666666666667</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17.69115031313677</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1098,37 +1126,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-4.67041998544801</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.3592630758036931</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-46704.1998544801</v>
+      </c>
+      <c r="J15" t="n">
+        <v>953295.8001455199</v>
+      </c>
+      <c r="K15" t="n">
+        <v>27889.68570026996</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.84615384615385</v>
+      </c>
+      <c r="M15" t="n">
+        <v>17.51564741607125</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1136,46 +1165,47 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-5.866862934555195</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.4889052445462663</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-58668.62934555195</v>
+      </c>
+      <c r="J16" t="n">
+        <v>941331.3706544481</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24266.53326035229</v>
+      </c>
+      <c r="L16" t="n">
+        <v>19.58333333333333</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11.60726693454057</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1183,11 +1213,11 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1196,33 +1226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-6.330034508684743</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.4869257314372879</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-63300.34508684743</v>
+      </c>
+      <c r="J17" t="n">
+        <v>936699.6549131526</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25979.23463035135</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17.61538461538462</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11.54759825240727</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1230,46 +1261,47 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-6.341057301551499</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.3522809611973055</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-63410.57301551499</v>
+      </c>
+      <c r="J18" t="n">
+        <v>936589.426984485</v>
+      </c>
+      <c r="K18" t="n">
+        <v>38270.51152955031</v>
+      </c>
+      <c r="L18" t="n">
+        <v>16</v>
+      </c>
+      <c r="M18" t="n">
+        <v>21.68910897774692</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1277,46 +1309,47 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-6.815346396176261</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5679455330146884</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-68153.46396176261</v>
+      </c>
+      <c r="J19" t="n">
+        <v>931846.5360382374</v>
+      </c>
+      <c r="K19" t="n">
+        <v>23972.27700040914</v>
+      </c>
+      <c r="L19" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11.89672514202716</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1328,42 +1361,43 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-7.183939302948931</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.4489962064343082</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-71839.39302948932</v>
+      </c>
+      <c r="J20" t="n">
+        <v>928160.6069705107</v>
+      </c>
+      <c r="K20" t="n">
+        <v>34294.48438768255</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.1875</v>
+      </c>
+      <c r="M20" t="n">
+        <v>21.78999824269666</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1375,42 +1409,43 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-7.23727685048841</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5169483464634579</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-72372.76850488409</v>
+      </c>
+      <c r="J21" t="n">
+        <v>927627.2314951159</v>
+      </c>
+      <c r="K21" t="n">
+        <v>28891.45427811755</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22.57142857142857</v>
+      </c>
+      <c r="M21" t="n">
+        <v>19.68863854830038</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1422,42 +1457,43 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-7.63473528627213</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.8483039206969034</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-76347.35286272131</v>
+      </c>
+      <c r="J22" t="n">
+        <v>923652.6471372787</v>
+      </c>
+      <c r="K22" t="n">
+        <v>17495.50794910837</v>
+      </c>
+      <c r="L22" t="n">
+        <v>21.88888888888889</v>
+      </c>
+      <c r="M22" t="n">
+        <v>15.68963678979108</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1469,42 +1505,43 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-7.936422850099917</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.6104940653923013</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-79364.22850099916</v>
+      </c>
+      <c r="J23" t="n">
+        <v>920635.7714990008</v>
+      </c>
+      <c r="K23" t="n">
+        <v>25811.96073847084</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20.23076923076923</v>
+      </c>
+      <c r="M23" t="n">
+        <v>12.82337322184402</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1516,7 +1553,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1525,33 +1562,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-10.86512793544232</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.6790704959651448</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-108651.2793544232</v>
+      </c>
+      <c r="J24" t="n">
+        <v>891348.7206455768</v>
+      </c>
+      <c r="K24" t="n">
+        <v>32977.65410559846</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22.50701282252684</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1563,42 +1601,43 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-10.99218369822135</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.7851559784443823</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-109921.8369822135</v>
+      </c>
+      <c r="J25" t="n">
+        <v>890078.1630177865</v>
+      </c>
+      <c r="K25" t="n">
+        <v>27212.55171287642</v>
+      </c>
+      <c r="L25" t="n">
+        <v>16</v>
+      </c>
+      <c r="M25" t="n">
+        <v>15.1470935574555</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1610,42 +1649,43 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-10.99967592426512</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.7856911374475083</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-109996.7592426512</v>
+      </c>
+      <c r="J26" t="n">
+        <v>890003.2407573488</v>
+      </c>
+      <c r="K26" t="n">
+        <v>27595.05473420181</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20</v>
+      </c>
+      <c r="M26" t="n">
+        <v>15.72402164590787</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1653,11 +1693,11 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1666,33 +1706,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-11.45837418620887</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.8814133989391437</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-114583.7418620887</v>
+      </c>
+      <c r="J27" t="n">
+        <v>885416.2581379113</v>
+      </c>
+      <c r="K27" t="n">
+        <v>25458.09200570522</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21.30769230769231</v>
+      </c>
+      <c r="M27" t="n">
+        <v>15.5915221425529</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1704,42 +1745,43 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-11.648989113784</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.1648989113784</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-116489.89113784</v>
+      </c>
+      <c r="J28" t="n">
+        <v>883510.10886216</v>
+      </c>
+      <c r="K28" t="n">
+        <v>20193.14892652744</v>
+      </c>
+      <c r="L28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>18.86474891788036</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1751,7 +1793,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1760,33 +1802,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-12.38289437648728</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.6879385764715158</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-123828.9437648728</v>
+      </c>
+      <c r="J29" t="n">
+        <v>876171.0562351272</v>
+      </c>
+      <c r="K29" t="n">
+        <v>36167.08023062248</v>
+      </c>
+      <c r="L29" t="n">
+        <v>15.72222222222222</v>
+      </c>
+      <c r="M29" t="n">
+        <v>22.44397800902465</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1803,37 +1846,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-12.66206551882301</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.7448273834601771</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-126620.6551882301</v>
+      </c>
+      <c r="J30" t="n">
+        <v>873379.3448117699</v>
+      </c>
+      <c r="K30" t="n">
+        <v>32385.81998613974</v>
+      </c>
+      <c r="L30" t="n">
+        <v>14.76470588235294</v>
+      </c>
+      <c r="M30" t="n">
+        <v>16.31745755313789</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1841,46 +1885,47 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-12.67804926191355</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-1.267804926191355</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-126780.4926191355</v>
+      </c>
+      <c r="J31" t="n">
+        <v>873219.5073808645</v>
+      </c>
+      <c r="K31" t="n">
+        <v>20161.07448234603</v>
+      </c>
+      <c r="L31" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>19.80976417757696</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1892,42 +1937,43 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-12.93974311407828</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.8626495409385518</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-129397.4311407828</v>
+      </c>
+      <c r="J32" t="n">
+        <v>870602.5688592172</v>
+      </c>
+      <c r="K32" t="n">
+        <v>28947.30615177735</v>
+      </c>
+      <c r="L32" t="n">
+        <v>15.93333333333333</v>
+      </c>
+      <c r="M32" t="n">
+        <v>17.00374035288645</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,11 +1981,11 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1948,33 +1994,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-14.2761422099178</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-1.42761422099178</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-142761.422099178</v>
+      </c>
+      <c r="J33" t="n">
+        <v>857238.577900822</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20030.50321867796</v>
+      </c>
+      <c r="L33" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>21.277338473426</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,46 +2029,47 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-14.40444054450456</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1.028888610321754</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-144044.4054450456</v>
+      </c>
+      <c r="J34" t="n">
+        <v>855955.5945549544</v>
+      </c>
+      <c r="K34" t="n">
+        <v>27184.22374098903</v>
+      </c>
+      <c r="L34" t="n">
+        <v>21</v>
+      </c>
+      <c r="M34" t="n">
+        <v>18.40006529595904</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2029,46 +2077,47 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-14.45309844881586</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1.032364174915419</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-144530.9844881586</v>
+      </c>
+      <c r="J35" t="n">
+        <v>855469.0155118414</v>
+      </c>
+      <c r="K35" t="n">
+        <v>26299.20836051588</v>
+      </c>
+      <c r="L35" t="n">
+        <v>16.07142857142857</v>
+      </c>
+      <c r="M35" t="n">
+        <v>18.35842538628097</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2076,46 +2125,47 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-15.00053251503573</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.9375332821897333</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-150005.3251503573</v>
+      </c>
+      <c r="J36" t="n">
+        <v>849994.6748496427</v>
+      </c>
+      <c r="K36" t="n">
+        <v>32274.04187334624</v>
+      </c>
+      <c r="L36" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="M36" t="n">
+        <v>23.86801710612795</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2123,11 +2173,11 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2136,33 +2186,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-15.09620890969138</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.161246839207029</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-150962.0890969138</v>
+      </c>
+      <c r="J37" t="n">
+        <v>849037.9109030862</v>
+      </c>
+      <c r="K37" t="n">
+        <v>24296.06215768283</v>
+      </c>
+      <c r="L37" t="n">
+        <v>18.07692307692308</v>
+      </c>
+      <c r="M37" t="n">
+        <v>17.96688941871773</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2183,33 +2234,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-15.38898849070203</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-1.282415707558502</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-153889.8849070203</v>
+      </c>
+      <c r="J38" t="n">
+        <v>846110.1150929797</v>
+      </c>
+      <c r="K38" t="n">
+        <v>23741.54475053718</v>
+      </c>
+      <c r="L38" t="n">
+        <v>13.41666666666667</v>
+      </c>
+      <c r="M38" t="n">
+        <v>23.83884195200748</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2217,46 +2269,47 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-15.84827927316228</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.9905174545726427</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-158482.7927316228</v>
+      </c>
+      <c r="J39" t="n">
+        <v>841517.2072683772</v>
+      </c>
+      <c r="K39" t="n">
+        <v>30571.29315572637</v>
+      </c>
+      <c r="L39" t="n">
+        <v>18.125</v>
+      </c>
+      <c r="M39" t="n">
+        <v>20.7674943920587</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2268,42 +2321,43 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-16.77176080926404</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-1.524705528114913</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-167717.6080926404</v>
+      </c>
+      <c r="J40" t="n">
+        <v>832282.3919073596</v>
+      </c>
+      <c r="K40" t="n">
+        <v>22067.9587486784</v>
+      </c>
+      <c r="L40" t="n">
+        <v>17.09090909090909</v>
+      </c>
+      <c r="M40" t="n">
+        <v>26.41903271231338</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2311,46 +2365,47 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-17.0848275730454</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.138988504869693</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-170848.275730454</v>
+      </c>
+      <c r="J41" t="n">
+        <v>829151.724269546</v>
+      </c>
+      <c r="K41" t="n">
+        <v>28326.93199669307</v>
+      </c>
+      <c r="L41" t="n">
+        <v>20.46666666666667</v>
+      </c>
+      <c r="M41" t="n">
+        <v>21.36313552310956</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2358,46 +2413,47 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-17.68691149514943</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-1.473909291262452</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-176869.1149514943</v>
+      </c>
+      <c r="J42" t="n">
+        <v>823130.8850485057</v>
+      </c>
+      <c r="K42" t="n">
+        <v>22614.61044015714</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12.41666666666667</v>
+      </c>
+      <c r="M42" t="n">
+        <v>21.50599789132269</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2405,46 +2461,47 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-18.10382995505653</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-1.645802723186957</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-181038.2995505653</v>
+      </c>
+      <c r="J43" t="n">
+        <v>818961.7004494347</v>
+      </c>
+      <c r="K43" t="n">
+        <v>21888.06823512285</v>
+      </c>
+      <c r="L43" t="n">
+        <v>19.54545454545455</v>
+      </c>
+      <c r="M43" t="n">
+        <v>27.59669713480431</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2456,42 +2513,43 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-19.39722198625688</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1.763383816932443</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-193972.2198625688</v>
+      </c>
+      <c r="J44" t="n">
+        <v>806027.7801374312</v>
+      </c>
+      <c r="K44" t="n">
+        <v>20919.83248094889</v>
+      </c>
+      <c r="L44" t="n">
+        <v>16.09090909090909</v>
+      </c>
+      <c r="M44" t="n">
+        <v>24.50716763789938</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2499,46 +2557,47 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-21.06717160321863</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-1.316698225201164</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-210671.7160321863</v>
+      </c>
+      <c r="J45" t="n">
+        <v>789328.2839678137</v>
+      </c>
+      <c r="K45" t="n">
+        <v>29265.2249244859</v>
+      </c>
+      <c r="L45" t="n">
+        <v>12.375</v>
+      </c>
+      <c r="M45" t="n">
+        <v>22.08298854694308</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2555,37 +2614,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-21.29841094143254</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-1.936219176493868</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-212984.1094143254</v>
+      </c>
+      <c r="J46" t="n">
+        <v>787015.8905856746</v>
+      </c>
+      <c r="K46" t="n">
+        <v>20651.5643842544</v>
+      </c>
+      <c r="L46" t="n">
+        <v>17.36363636363636</v>
+      </c>
+      <c r="M46" t="n">
+        <v>26.28782759303494</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/9432.T_settings.xlsx
+++ b/9432.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F2" t="n">
-        <v>7.612015055460088</v>
+        <v>6.930271831709751</v>
       </c>
       <c r="G2" t="n">
         <v>14</v>
       </c>
       <c r="H2" t="n">
-        <v>0.543715361104292</v>
+        <v>0.4950194165506965</v>
       </c>
       <c r="I2" t="n">
-        <v>76120.15055460087</v>
+        <v>69302.71831709752</v>
       </c>
       <c r="J2" t="n">
-        <v>1076120.150554601</v>
+        <v>1069302.718317098</v>
       </c>
       <c r="K2" t="n">
-        <v>29308.54019465601</v>
+        <v>29261.49262969942</v>
       </c>
       <c r="L2" t="n">
-        <v>18.85714285714286</v>
+        <v>19.35714285714286</v>
       </c>
       <c r="M2" t="n">
-        <v>6.352170559005449</v>
+        <v>6.945459406534109</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,28 +557,28 @@
         <v>38.46153846153847</v>
       </c>
       <c r="F3" t="n">
-        <v>4.675039817605575</v>
+        <v>5.176401376899006</v>
       </c>
       <c r="G3" t="n">
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3596184475081212</v>
+        <v>0.3981847212999235</v>
       </c>
       <c r="I3" t="n">
-        <v>46750.39817605575</v>
+        <v>51764.01376899006</v>
       </c>
       <c r="J3" t="n">
-        <v>1046750.398176056</v>
+        <v>1051764.01376899</v>
       </c>
       <c r="K3" t="n">
-        <v>27510.22189543437</v>
+        <v>27545.08614579137</v>
       </c>
       <c r="L3" t="n">
-        <v>22.76923076923077</v>
+        <v>22.84615384615385</v>
       </c>
       <c r="M3" t="n">
-        <v>9.376444474402588</v>
+        <v>8.942380593359402</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -605,28 +605,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>3.007288486012688</v>
+        <v>2.35469090240947</v>
       </c>
       <c r="G4" t="n">
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2506073738343907</v>
+        <v>0.1962242418674558</v>
       </c>
       <c r="I4" t="n">
-        <v>30072.88486012688</v>
+        <v>23546.9090240947</v>
       </c>
       <c r="J4" t="n">
-        <v>1030072.884860127</v>
+        <v>1023546.909024095</v>
       </c>
       <c r="K4" t="n">
-        <v>25845.40753178055</v>
+        <v>25799.53841344354</v>
       </c>
       <c r="L4" t="n">
-        <v>25.33333333333333</v>
+        <v>25.91666666666667</v>
       </c>
       <c r="M4" t="n">
-        <v>11.63256599361263</v>
+        <v>12.19239785165254</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>1.385650723548699</v>
+        <v>1.385651590271154</v>
       </c>
       <c r="G5" t="n">
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1385650723548699</v>
+        <v>0.1385651590271154</v>
       </c>
       <c r="I5" t="n">
-        <v>13856.50723548699</v>
+        <v>13856.51590271154</v>
       </c>
       <c r="J5" t="n">
-        <v>1013856.507235487</v>
+        <v>1013856.515902712</v>
       </c>
       <c r="K5" t="n">
-        <v>20566.83720297617</v>
+        <v>20566.83705790085</v>
       </c>
       <c r="L5" t="n">
         <v>20.1</v>
       </c>
       <c r="M5" t="n">
-        <v>10.42809822239414</v>
+        <v>10.42809724614204</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>38.46153846153847</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.569661661519506</v>
+        <v>-0.09348542189579456</v>
       </c>
       <c r="G6" t="n">
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.04382012780919277</v>
+        <v>-0.007191186299676505</v>
       </c>
       <c r="I6" t="n">
-        <v>-5696.61661519506</v>
+        <v>-934.8542189579457</v>
       </c>
       <c r="J6" t="n">
-        <v>994303.3833848049</v>
+        <v>999065.1457810421</v>
       </c>
       <c r="K6" t="n">
-        <v>28454.96331526446</v>
+        <v>28489.7648233968</v>
       </c>
       <c r="L6" t="n">
-        <v>22.30769230769231</v>
+        <v>22.38461538461538</v>
       </c>
       <c r="M6" t="n">
-        <v>16.49227970951264</v>
+        <v>16.09233284384389</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.005090074573061</v>
+        <v>-2.005043780755904</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2005090074573061</v>
+        <v>-0.2005043780755904</v>
       </c>
       <c r="I7" t="n">
-        <v>-20050.90074573061</v>
+        <v>-20050.43780755904</v>
       </c>
       <c r="J7" t="n">
-        <v>979949.0992542694</v>
+        <v>979949.562192441</v>
       </c>
       <c r="K7" t="n">
-        <v>19701.08449518263</v>
+        <v>19701.08818764066</v>
       </c>
       <c r="L7" t="n">
         <v>16.3</v>
       </c>
       <c r="M7" t="n">
-        <v>11.19042233991907</v>
+        <v>11.19040464648023</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.428816998501623</v>
+        <v>-2.428848508143704</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2428816998501623</v>
+        <v>-0.2428848508143704</v>
       </c>
       <c r="I8" t="n">
-        <v>-24288.16998501623</v>
+        <v>-24288.48508143704</v>
       </c>
       <c r="J8" t="n">
-        <v>975711.8300149838</v>
+        <v>975711.514918563</v>
       </c>
       <c r="K8" t="n">
-        <v>21601.66673592353</v>
+        <v>21601.6612851537</v>
       </c>
       <c r="L8" t="n">
         <v>26</v>
       </c>
       <c r="M8" t="n">
-        <v>14.51076576711587</v>
+        <v>14.51078440205096</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -829,44 +829,44 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.79572114116723</v>
+        <v>-2.597214057765226</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.279572114116723</v>
+        <v>-0.1623258786103266</v>
       </c>
       <c r="I9" t="n">
-        <v>-27957.2114116723</v>
+        <v>-25972.14057765226</v>
       </c>
       <c r="J9" t="n">
-        <v>972042.7885883277</v>
+        <v>974027.8594223477</v>
       </c>
       <c r="K9" t="n">
-        <v>20127.9525420345</v>
+        <v>35002.21272239255</v>
       </c>
       <c r="L9" t="n">
-        <v>20.8</v>
+        <v>20.8125</v>
       </c>
       <c r="M9" t="n">
-        <v>12.3088808570559</v>
+        <v>20.01058969973888</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -877,44 +877,44 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.061452554666938</v>
+        <v>-2.795721621403762</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1913407846666836</v>
+        <v>-0.2795721621403762</v>
       </c>
       <c r="I10" t="n">
-        <v>-30614.52554666938</v>
+        <v>-27957.21621403762</v>
       </c>
       <c r="J10" t="n">
-        <v>969385.4744533306</v>
+        <v>972042.7837859624</v>
       </c>
       <c r="K10" t="n">
-        <v>34968.14711857103</v>
+        <v>20127.95151965796</v>
       </c>
       <c r="L10" t="n">
-        <v>20.75</v>
+        <v>20.8</v>
       </c>
       <c r="M10" t="n">
-        <v>20.3918454117041</v>
+        <v>12.30888090195078</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.661507446657808</v>
+        <v>-3.661467691991117</v>
       </c>
       <c r="G11" t="n">
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4068341607397564</v>
+        <v>-0.4068297435545686</v>
       </c>
       <c r="I11" t="n">
-        <v>-36615.07446657808</v>
+        <v>-36614.67691991117</v>
       </c>
       <c r="J11" t="n">
-        <v>963384.9255334219</v>
+        <v>963385.3230800888</v>
       </c>
       <c r="K11" t="n">
-        <v>17854.54448185549</v>
+        <v>17854.54666728154</v>
       </c>
       <c r="L11" t="n">
         <v>21.11111111111111</v>
       </c>
       <c r="M11" t="n">
-        <v>13.14054133261224</v>
+        <v>13.14051406605002</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -973,44 +973,44 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>26.66666666666667</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.775275142113515</v>
+        <v>-3.937061083305883</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2516850094742343</v>
+        <v>-0.2812186488075631</v>
       </c>
       <c r="I12" t="n">
-        <v>-37752.75142113515</v>
+        <v>-39370.61083305883</v>
       </c>
       <c r="J12" t="n">
-        <v>962247.2485788648</v>
+        <v>960629.3891669412</v>
       </c>
       <c r="K12" t="n">
-        <v>31867.63767788429</v>
+        <v>29342.33965778925</v>
       </c>
       <c r="L12" t="n">
-        <v>16.8</v>
+        <v>21.21428571428572</v>
       </c>
       <c r="M12" t="n">
-        <v>17.71773189272497</v>
+        <v>17.72131352678771</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1021,44 +1021,44 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>42.85714285714285</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.937079606202687</v>
+        <v>-4.384938980027428</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2812199718716205</v>
+        <v>-0.2923292653351618</v>
       </c>
       <c r="I13" t="n">
-        <v>-39370.79606202687</v>
+        <v>-43849.38980027428</v>
       </c>
       <c r="J13" t="n">
-        <v>960629.2039379731</v>
+        <v>956150.6101997257</v>
       </c>
       <c r="K13" t="n">
-        <v>29342.33853733689</v>
+        <v>31810.02179657488</v>
       </c>
       <c r="L13" t="n">
-        <v>21.21428571428572</v>
+        <v>17.26666666666667</v>
       </c>
       <c r="M13" t="n">
-        <v>17.721322054217</v>
+        <v>18.23904036517322</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.669751984537545</v>
+        <v>-4.669752155357703</v>
       </c>
       <c r="G14" t="n">
         <v>15</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3113167989691696</v>
+        <v>-0.3113168103571802</v>
       </c>
       <c r="I14" t="n">
-        <v>-46697.51984537544</v>
+        <v>-46697.52155357704</v>
       </c>
       <c r="J14" t="n">
-        <v>953302.4801546246</v>
+        <v>953302.478446423</v>
       </c>
       <c r="K14" t="n">
-        <v>31357.20834079523</v>
+        <v>31357.20723958407</v>
       </c>
       <c r="L14" t="n">
         <v>18.26666666666667</v>
       </c>
       <c r="M14" t="n">
-        <v>17.69115031313677</v>
+        <v>17.69115025273696</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>38.46153846153847</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.67041998544801</v>
+        <v>-5.274417432118405</v>
       </c>
       <c r="G15" t="n">
         <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3592630758036931</v>
+        <v>-0.4057244178552619</v>
       </c>
       <c r="I15" t="n">
-        <v>-46704.1998544801</v>
+        <v>-52744.17432118405</v>
       </c>
       <c r="J15" t="n">
-        <v>953295.8001455199</v>
+        <v>947255.8256788159</v>
       </c>
       <c r="K15" t="n">
-        <v>27889.68570026996</v>
+        <v>27845.05702944988</v>
       </c>
       <c r="L15" t="n">
-        <v>22.84615384615385</v>
+        <v>23.38461538461538</v>
       </c>
       <c r="M15" t="n">
-        <v>17.51564741607125</v>
+        <v>18.03823368118193</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.866862934555195</v>
+        <v>-5.86687103439084</v>
       </c>
       <c r="G16" t="n">
         <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4889052445462663</v>
+        <v>-0.48890591953257</v>
       </c>
       <c r="I16" t="n">
-        <v>-58668.62934555195</v>
+        <v>-58668.7103439084</v>
       </c>
       <c r="J16" t="n">
-        <v>941331.3706544481</v>
+        <v>941331.2896560916</v>
       </c>
       <c r="K16" t="n">
-        <v>24266.53326035229</v>
+        <v>24266.5321019888</v>
       </c>
       <c r="L16" t="n">
         <v>19.58333333333333</v>
       </c>
       <c r="M16" t="n">
-        <v>11.60726693454057</v>
+        <v>11.60725768972151</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1217,40 +1217,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>38.46153846153847</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.330034508684743</v>
+        <v>-6.815330442106514</v>
       </c>
       <c r="G17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4869257314372879</v>
+        <v>-0.5679442035088761</v>
       </c>
       <c r="I17" t="n">
-        <v>-63300.34508684743</v>
+        <v>-68153.30442106514</v>
       </c>
       <c r="J17" t="n">
-        <v>936699.6549131526</v>
+        <v>931846.6955789349</v>
       </c>
       <c r="K17" t="n">
-        <v>25979.23463035135</v>
+        <v>23972.27917040265</v>
       </c>
       <c r="L17" t="n">
-        <v>17.61538461538462</v>
+        <v>15.25</v>
       </c>
       <c r="M17" t="n">
-        <v>11.54759825240727</v>
+        <v>11.89671612974397</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>27.77777777777778</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.341057301551499</v>
+        <v>-6.934460451564065</v>
       </c>
       <c r="G18" t="n">
         <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3522809611973055</v>
+        <v>-0.3852478028646703</v>
       </c>
       <c r="I18" t="n">
-        <v>-63410.57301551499</v>
+        <v>-69344.60451564065</v>
       </c>
       <c r="J18" t="n">
-        <v>936589.426984485</v>
+        <v>930655.3954843594</v>
       </c>
       <c r="K18" t="n">
-        <v>38270.51152955031</v>
+        <v>38213.9573200935</v>
       </c>
       <c r="L18" t="n">
-        <v>16</v>
+        <v>16.38888888888889</v>
       </c>
       <c r="M18" t="n">
-        <v>21.68910897774692</v>
+        <v>22.18526358925615</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1309,44 +1309,44 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.815346396176261</v>
+        <v>-7.237264557393698</v>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5679455330146884</v>
+        <v>-0.5169474683852642</v>
       </c>
       <c r="I19" t="n">
-        <v>-68153.46396176261</v>
+        <v>-72372.64557393698</v>
       </c>
       <c r="J19" t="n">
-        <v>931846.5360382374</v>
+        <v>927627.354426063</v>
       </c>
       <c r="K19" t="n">
-        <v>23972.27700040914</v>
+        <v>28891.45652635384</v>
       </c>
       <c r="L19" t="n">
-        <v>15.25</v>
+        <v>22.57142857142857</v>
       </c>
       <c r="M19" t="n">
-        <v>11.89672514202716</v>
+        <v>19.68863015198105</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1361,40 +1361,40 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.5</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.183939302948931</v>
+        <v>-7.634698417005327</v>
       </c>
       <c r="G20" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4489962064343082</v>
+        <v>-0.848299824111703</v>
       </c>
       <c r="I20" t="n">
-        <v>-71839.39302948932</v>
+        <v>-76346.98417005327</v>
       </c>
       <c r="J20" t="n">
-        <v>928160.6069705107</v>
+        <v>923653.0158299467</v>
       </c>
       <c r="K20" t="n">
-        <v>34294.48438768255</v>
+        <v>17495.50922218085</v>
       </c>
       <c r="L20" t="n">
-        <v>22.1875</v>
+        <v>21.88888888888889</v>
       </c>
       <c r="M20" t="n">
-        <v>21.78999824269666</v>
+        <v>15.68961146060887</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1414,35 +1414,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>35.71428571428572</v>
+        <v>37.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.23727685048841</v>
+        <v>-7.771995790407516</v>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5169483464634579</v>
+        <v>-0.4857497369004697</v>
       </c>
       <c r="I21" t="n">
-        <v>-72372.76850488409</v>
+        <v>-77719.95790407516</v>
       </c>
       <c r="J21" t="n">
-        <v>927627.2314951159</v>
+        <v>922280.0420959248</v>
       </c>
       <c r="K21" t="n">
-        <v>28891.45427811755</v>
+        <v>34250.8598655864</v>
       </c>
       <c r="L21" t="n">
-        <v>22.57142857142857</v>
+        <v>22.625</v>
       </c>
       <c r="M21" t="n">
-        <v>19.68863854830038</v>
+        <v>22.2855040513822</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1453,44 +1453,44 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>22.22222222222222</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.63473528627213</v>
+        <v>-7.936408452801929</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8483039206969034</v>
+        <v>-0.6104929579078407</v>
       </c>
       <c r="I22" t="n">
-        <v>-76347.35286272131</v>
+        <v>-79364.0845280193</v>
       </c>
       <c r="J22" t="n">
-        <v>923652.6471372787</v>
+        <v>920635.9154719807</v>
       </c>
       <c r="K22" t="n">
-        <v>17495.50794910837</v>
+        <v>25811.96149643771</v>
       </c>
       <c r="L22" t="n">
-        <v>21.88888888888889</v>
+        <v>20.23076923076923</v>
       </c>
       <c r="M22" t="n">
-        <v>15.68963678979108</v>
+        <v>12.82336418678732</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1501,11 +1501,11 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1514,31 +1514,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>38.46153846153847</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.936422850099917</v>
+        <v>-8.323728243397955</v>
       </c>
       <c r="G23" t="n">
         <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6104940653923013</v>
+        <v>-0.6402867879536889</v>
       </c>
       <c r="I23" t="n">
-        <v>-79364.22850099916</v>
+        <v>-83237.28243397956</v>
       </c>
       <c r="J23" t="n">
-        <v>920635.7714990008</v>
+        <v>916762.7175660204</v>
       </c>
       <c r="K23" t="n">
-        <v>25811.96073847084</v>
+        <v>25874.95974190101</v>
       </c>
       <c r="L23" t="n">
-        <v>20.23076923076923</v>
+        <v>17.69230769230769</v>
       </c>
       <c r="M23" t="n">
-        <v>12.82337322184402</v>
+        <v>13.43024372822304</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -1565,28 +1565,28 @@
         <v>31.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.86512793544232</v>
+        <v>-10.4382861375006</v>
       </c>
       <c r="G24" t="n">
         <v>16</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6790704959651448</v>
+        <v>-0.6523928835937877</v>
       </c>
       <c r="I24" t="n">
-        <v>-108651.2793544232</v>
+        <v>-104382.861375006</v>
       </c>
       <c r="J24" t="n">
-        <v>891348.7206455768</v>
+        <v>895617.138624994</v>
       </c>
       <c r="K24" t="n">
-        <v>32977.65410559846</v>
+        <v>33018.51035728429</v>
       </c>
       <c r="L24" t="n">
-        <v>20.75</v>
+        <v>20.8125</v>
       </c>
       <c r="M24" t="n">
-        <v>22.50701282252684</v>
+        <v>22.13588697302739</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,28 +1613,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.99218369822135</v>
+        <v>-10.99217785909338</v>
       </c>
       <c r="G25" t="n">
         <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7851559784443823</v>
+        <v>-0.7851555613638127</v>
       </c>
       <c r="I25" t="n">
-        <v>-109921.8369822135</v>
+        <v>-109921.7785909338</v>
       </c>
       <c r="J25" t="n">
-        <v>890078.1630177865</v>
+        <v>890078.2214090662</v>
       </c>
       <c r="K25" t="n">
-        <v>27212.55171287642</v>
+        <v>27212.5522385948</v>
       </c>
       <c r="L25" t="n">
         <v>16</v>
       </c>
       <c r="M25" t="n">
-        <v>15.1470935574555</v>
+        <v>15.14708528265348</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -1661,28 +1661,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.99967592426512</v>
+        <v>-10.99966200601182</v>
       </c>
       <c r="G26" t="n">
         <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7856911374475083</v>
+        <v>-0.7856901432865583</v>
       </c>
       <c r="I26" t="n">
-        <v>-109996.7592426512</v>
+        <v>-109996.6200601181</v>
       </c>
       <c r="J26" t="n">
-        <v>890003.2407573488</v>
+        <v>890003.3799398819</v>
       </c>
       <c r="K26" t="n">
-        <v>27595.05473420181</v>
+        <v>27595.05577101659</v>
       </c>
       <c r="L26" t="n">
         <v>20</v>
       </c>
       <c r="M26" t="n">
-        <v>15.72402164590787</v>
+        <v>15.72401291147674</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1709,28 +1709,28 @@
         <v>30.76923076923077</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.45837418620887</v>
+        <v>-11.4583683353979</v>
       </c>
       <c r="G27" t="n">
         <v>13</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8814133989391437</v>
+        <v>-0.8814129488767617</v>
       </c>
       <c r="I27" t="n">
-        <v>-114583.7418620887</v>
+        <v>-114583.683353979</v>
       </c>
       <c r="J27" t="n">
-        <v>885416.2581379113</v>
+        <v>885416.316646021</v>
       </c>
       <c r="K27" t="n">
-        <v>25458.09200570522</v>
+        <v>25458.09221984406</v>
       </c>
       <c r="L27" t="n">
         <v>21.30769230769231</v>
       </c>
       <c r="M27" t="n">
-        <v>15.5915221425529</v>
+        <v>15.59151387079806</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>30</v>
       </c>
       <c r="F28" t="n">
-        <v>-11.648989113784</v>
+        <v>-11.64900762637112</v>
       </c>
       <c r="G28" t="n">
         <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1648989113784</v>
+        <v>-1.164900762637112</v>
       </c>
       <c r="I28" t="n">
-        <v>-116489.89113784</v>
+        <v>-116490.0762637112</v>
       </c>
       <c r="J28" t="n">
-        <v>883510.10886216</v>
+        <v>883509.9237362888</v>
       </c>
       <c r="K28" t="n">
-        <v>20193.14892652744</v>
+        <v>20193.14563987428</v>
       </c>
       <c r="L28" t="n">
         <v>15.6</v>
       </c>
       <c r="M28" t="n">
-        <v>18.86474891788036</v>
+        <v>18.86475808107364</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1793,40 +1793,40 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22.22222222222222</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="F29" t="n">
-        <v>-12.38289437648728</v>
+        <v>-12.66205145994868</v>
       </c>
       <c r="G29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6879385764715158</v>
+        <v>-0.7448265564675696</v>
       </c>
       <c r="I29" t="n">
-        <v>-123828.9437648728</v>
+        <v>-126620.5145994868</v>
       </c>
       <c r="J29" t="n">
-        <v>876171.0562351272</v>
+        <v>873379.4854005132</v>
       </c>
       <c r="K29" t="n">
-        <v>36167.08023062248</v>
+        <v>32385.82001750978</v>
       </c>
       <c r="L29" t="n">
-        <v>15.72222222222222</v>
+        <v>14.76470588235294</v>
       </c>
       <c r="M29" t="n">
-        <v>22.44397800902465</v>
+        <v>16.31743231292997</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1837,44 +1837,44 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>23.52941176470588</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
-        <v>-12.66206551882301</v>
+        <v>-12.67806755887705</v>
       </c>
       <c r="G30" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7448273834601771</v>
+        <v>-1.267806755887705</v>
       </c>
       <c r="I30" t="n">
-        <v>-126620.6551882301</v>
+        <v>-126780.6755887705</v>
       </c>
       <c r="J30" t="n">
-        <v>873379.3448117699</v>
+        <v>873219.3244112295</v>
       </c>
       <c r="K30" t="n">
-        <v>32385.81998613974</v>
+        <v>20161.07120241359</v>
       </c>
       <c r="L30" t="n">
-        <v>14.76470588235294</v>
+        <v>15.8</v>
       </c>
       <c r="M30" t="n">
-        <v>16.31745755313789</v>
+        <v>19.80977323404281</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1885,44 +1885,44 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F31" t="n">
-        <v>-12.67804926191355</v>
+        <v>-12.93804195005528</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.267804926191355</v>
+        <v>-0.7187801083364046</v>
       </c>
       <c r="I31" t="n">
-        <v>-126780.4926191355</v>
+        <v>-129380.4195005528</v>
       </c>
       <c r="J31" t="n">
-        <v>873219.5073808645</v>
+        <v>870619.5804994472</v>
       </c>
       <c r="K31" t="n">
-        <v>20161.07448234603</v>
+        <v>36102.33318385724</v>
       </c>
       <c r="L31" t="n">
-        <v>15.8</v>
+        <v>16.11111111111111</v>
       </c>
       <c r="M31" t="n">
-        <v>19.80976417757696</v>
+        <v>22.93534999392768</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>26.66666666666667</v>
       </c>
       <c r="F32" t="n">
-        <v>-12.93974311407828</v>
+        <v>-12.9397374027149</v>
       </c>
       <c r="G32" t="n">
         <v>15</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8626495409385518</v>
+        <v>-0.8626491601809936</v>
       </c>
       <c r="I32" t="n">
-        <v>-129397.4311407828</v>
+        <v>-129397.3740271491</v>
       </c>
       <c r="J32" t="n">
-        <v>870602.5688592172</v>
+        <v>870602.6259728509</v>
       </c>
       <c r="K32" t="n">
-        <v>28947.30615177735</v>
+        <v>28947.30679129982</v>
       </c>
       <c r="L32" t="n">
         <v>15.93333333333333</v>
       </c>
       <c r="M32" t="n">
-        <v>17.00374035288645</v>
+        <v>17.00373225914345</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>-14.2761422099178</v>
+        <v>-14.27614245817226</v>
       </c>
       <c r="G33" t="n">
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.42761422099178</v>
+        <v>-1.427614245817226</v>
       </c>
       <c r="I33" t="n">
-        <v>-142761.422099178</v>
+        <v>-142761.4245817226</v>
       </c>
       <c r="J33" t="n">
-        <v>857238.577900822</v>
+        <v>857238.5754182774</v>
       </c>
       <c r="K33" t="n">
-        <v>20030.50321867796</v>
+        <v>20030.50218515884</v>
       </c>
       <c r="L33" t="n">
         <v>17.8</v>
       </c>
       <c r="M33" t="n">
-        <v>21.277338473426</v>
+        <v>21.27733109701008</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,28 +2045,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F34" t="n">
-        <v>-14.40444054450456</v>
+        <v>-14.40443488836899</v>
       </c>
       <c r="G34" t="n">
         <v>14</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.028888610321754</v>
+        <v>-1.02888820631207</v>
       </c>
       <c r="I34" t="n">
-        <v>-144044.4054450456</v>
+        <v>-144044.3488836898</v>
       </c>
       <c r="J34" t="n">
-        <v>855955.5945549544</v>
+        <v>855955.6511163102</v>
       </c>
       <c r="K34" t="n">
-        <v>27184.22374098903</v>
+        <v>27184.22406919028</v>
       </c>
       <c r="L34" t="n">
         <v>21</v>
       </c>
       <c r="M34" t="n">
-        <v>18.40006529595904</v>
+        <v>18.40005729943223</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2093,28 +2093,28 @@
         <v>21.42857142857143</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.45309844881586</v>
+        <v>-14.45310058640433</v>
       </c>
       <c r="G35" t="n">
         <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.032364174915419</v>
+        <v>-1.032364327600309</v>
       </c>
       <c r="I35" t="n">
-        <v>-144530.9844881586</v>
+        <v>-144531.0058640433</v>
       </c>
       <c r="J35" t="n">
-        <v>855469.0155118414</v>
+        <v>855468.9941359567</v>
       </c>
       <c r="K35" t="n">
-        <v>26299.20836051588</v>
+        <v>26299.20665406362</v>
       </c>
       <c r="L35" t="n">
         <v>16.07142857142857</v>
       </c>
       <c r="M35" t="n">
-        <v>18.35842538628097</v>
+        <v>18.35841573974455</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2134,35 +2134,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31.25</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="F36" t="n">
-        <v>-15.00053251503573</v>
+        <v>-15.09620415593793</v>
       </c>
       <c r="G36" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9375332821897333</v>
+        <v>-1.161246473533687</v>
       </c>
       <c r="I36" t="n">
-        <v>-150005.3251503573</v>
+        <v>-150962.0415593793</v>
       </c>
       <c r="J36" t="n">
-        <v>849994.6748496427</v>
+        <v>849037.9584406207</v>
       </c>
       <c r="K36" t="n">
-        <v>32274.04187334624</v>
+        <v>24296.06030840611</v>
       </c>
       <c r="L36" t="n">
-        <v>21.875</v>
+        <v>18.07692307692308</v>
       </c>
       <c r="M36" t="n">
-        <v>23.86801710612795</v>
+        <v>17.966873083105</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2182,35 +2182,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>23.07692307692308</v>
+        <v>31.25</v>
       </c>
       <c r="F37" t="n">
-        <v>-15.09620890969138</v>
+        <v>-15.53909129319171</v>
       </c>
       <c r="G37" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.161246839207029</v>
+        <v>-0.971193205824482</v>
       </c>
       <c r="I37" t="n">
-        <v>-150962.0890969138</v>
+        <v>-155390.9129319171</v>
       </c>
       <c r="J37" t="n">
-        <v>849037.9109030862</v>
+        <v>844609.0870680829</v>
       </c>
       <c r="K37" t="n">
-        <v>24296.06215768283</v>
+        <v>32221.89786697969</v>
       </c>
       <c r="L37" t="n">
-        <v>18.07692307692308</v>
+        <v>22.3125</v>
       </c>
       <c r="M37" t="n">
-        <v>17.96688941871773</v>
+        <v>24.35035745778431</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2221,44 +2221,44 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>-15.38898849070203</v>
+        <v>-15.84827850334334</v>
       </c>
       <c r="G38" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.282415707558502</v>
+        <v>-0.9905174064589585</v>
       </c>
       <c r="I38" t="n">
-        <v>-153889.8849070203</v>
+        <v>-158482.7850334333</v>
       </c>
       <c r="J38" t="n">
-        <v>846110.1150929797</v>
+        <v>841517.2149665667</v>
       </c>
       <c r="K38" t="n">
-        <v>23741.54475053718</v>
+        <v>30571.28991622233</v>
       </c>
       <c r="L38" t="n">
-        <v>13.41666666666667</v>
+        <v>18.125</v>
       </c>
       <c r="M38" t="n">
-        <v>23.83884195200748</v>
+        <v>20.76747687669996</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2269,44 +2269,44 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>-15.84827927316228</v>
+        <v>-15.92507722321784</v>
       </c>
       <c r="G39" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9905174545726427</v>
+        <v>-1.327089768601486</v>
       </c>
       <c r="I39" t="n">
-        <v>-158482.7927316228</v>
+        <v>-159250.7722321784</v>
       </c>
       <c r="J39" t="n">
-        <v>841517.2072683772</v>
+        <v>840749.2277678216</v>
       </c>
       <c r="K39" t="n">
-        <v>30571.29315572637</v>
+        <v>23713.75488241663</v>
       </c>
       <c r="L39" t="n">
-        <v>18.125</v>
+        <v>14</v>
       </c>
       <c r="M39" t="n">
-        <v>20.7674943920587</v>
+        <v>24.32137599799452</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F40" t="n">
-        <v>-16.77176080926404</v>
+        <v>-16.37320084564653</v>
       </c>
       <c r="G40" t="n">
         <v>11</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.524705528114913</v>
+        <v>-1.488472804149685</v>
       </c>
       <c r="I40" t="n">
-        <v>-167717.6080926404</v>
+        <v>-163732.0084564653</v>
       </c>
       <c r="J40" t="n">
-        <v>832282.3919073596</v>
+        <v>836267.9915435347</v>
       </c>
       <c r="K40" t="n">
-        <v>22067.9587486784</v>
+        <v>22088.87441719541</v>
       </c>
       <c r="L40" t="n">
-        <v>17.09090909090909</v>
+        <v>17.18181818181818</v>
       </c>
       <c r="M40" t="n">
-        <v>26.41903271231338</v>
+        <v>26.06664925406819</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>26.66666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>-17.0848275730454</v>
+        <v>-17.08480857980312</v>
       </c>
       <c r="G41" t="n">
         <v>15</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.138988504869693</v>
+        <v>-1.138987238653541</v>
       </c>
       <c r="I41" t="n">
-        <v>-170848.275730454</v>
+        <v>-170848.0857980312</v>
       </c>
       <c r="J41" t="n">
-        <v>829151.724269546</v>
+        <v>829151.9142019688</v>
       </c>
       <c r="K41" t="n">
-        <v>28326.93199669307</v>
+        <v>28326.93285692806</v>
       </c>
       <c r="L41" t="n">
         <v>20.46666666666667</v>
       </c>
       <c r="M41" t="n">
-        <v>21.36313552310956</v>
+        <v>21.3631117716293</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>16.66666666666666</v>
       </c>
       <c r="F42" t="n">
-        <v>-17.68691149514943</v>
+        <v>-17.68687913269799</v>
       </c>
       <c r="G42" t="n">
         <v>12</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.473909291262452</v>
+        <v>-1.473906594391499</v>
       </c>
       <c r="I42" t="n">
-        <v>-176869.1149514943</v>
+        <v>-176868.7913269799</v>
       </c>
       <c r="J42" t="n">
-        <v>823130.8850485057</v>
+        <v>823131.2086730201</v>
       </c>
       <c r="K42" t="n">
-        <v>22614.61044015714</v>
+        <v>22614.61602115785</v>
       </c>
       <c r="L42" t="n">
         <v>12.41666666666667</v>
       </c>
       <c r="M42" t="n">
-        <v>21.50599789132269</v>
+        <v>21.50597227683519</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,28 +2477,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F43" t="n">
-        <v>-18.10382995505653</v>
+        <v>-18.62272355341042</v>
       </c>
       <c r="G43" t="n">
         <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.645802723186957</v>
+        <v>-1.692974868491856</v>
       </c>
       <c r="I43" t="n">
-        <v>-181038.2995505653</v>
+        <v>-186227.2355341042</v>
       </c>
       <c r="J43" t="n">
-        <v>818961.7004494347</v>
+        <v>813772.7644658958</v>
       </c>
       <c r="K43" t="n">
-        <v>21888.06823512285</v>
+        <v>21860.8250557713</v>
       </c>
       <c r="L43" t="n">
-        <v>19.54545454545455</v>
+        <v>20.18181818181818</v>
       </c>
       <c r="M43" t="n">
-        <v>27.59669713480431</v>
+        <v>28.05542262631064</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2525,28 +2525,28 @@
         <v>18.18181818181818</v>
       </c>
       <c r="F44" t="n">
-        <v>-19.39722198625688</v>
+        <v>-19.39720336715574</v>
       </c>
       <c r="G44" t="n">
         <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.763383816932443</v>
+        <v>-1.763382124286886</v>
       </c>
       <c r="I44" t="n">
-        <v>-193972.2198625688</v>
+        <v>-193972.0336715574</v>
       </c>
       <c r="J44" t="n">
-        <v>806027.7801374312</v>
+        <v>806027.9663284426</v>
       </c>
       <c r="K44" t="n">
-        <v>20919.83248094889</v>
+        <v>20919.8361474382</v>
       </c>
       <c r="L44" t="n">
         <v>16.09090909090909</v>
       </c>
       <c r="M44" t="n">
-        <v>24.50716763789938</v>
+        <v>24.50714986486506</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>18.75</v>
       </c>
       <c r="F45" t="n">
-        <v>-21.06717160321863</v>
+        <v>-21.06715346908737</v>
       </c>
       <c r="G45" t="n">
         <v>16</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.316698225201164</v>
+        <v>-1.316697091817961</v>
       </c>
       <c r="I45" t="n">
-        <v>-210671.7160321863</v>
+        <v>-210671.5346908737</v>
       </c>
       <c r="J45" t="n">
-        <v>789328.2839678137</v>
+        <v>789328.4653091263</v>
       </c>
       <c r="K45" t="n">
-        <v>29265.2249244859</v>
+        <v>29265.22654221375</v>
       </c>
       <c r="L45" t="n">
         <v>12.375</v>
       </c>
       <c r="M45" t="n">
-        <v>22.08298854694308</v>
+        <v>22.08296504572631</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>18.18181818181818</v>
       </c>
       <c r="F46" t="n">
-        <v>-21.29841094143254</v>
+        <v>-21.29838786575478</v>
       </c>
       <c r="G46" t="n">
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.936219176493868</v>
+        <v>-1.93621707870498</v>
       </c>
       <c r="I46" t="n">
-        <v>-212984.1094143254</v>
+        <v>-212983.8786575478</v>
       </c>
       <c r="J46" t="n">
-        <v>787015.8905856746</v>
+        <v>787016.1213424522</v>
       </c>
       <c r="K46" t="n">
-        <v>20651.5643842544</v>
+        <v>20651.56631573392</v>
       </c>
       <c r="L46" t="n">
         <v>17.36363636363636</v>
       </c>
       <c r="M46" t="n">
-        <v>26.28782759303494</v>
+        <v>26.28780565384166</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
